--- a/sheets/조재수대금교본/검수/어디로 가야하나.xlsx
+++ b/sheets/조재수대금교본/검수/어디로 가야하나.xlsx
@@ -2284,30 +2284,19 @@
       <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∼
-‹</t>
+          <t xml:space="preserve">潢∼</t>
         </is>
       </c>
       <c r="E5" s="24"/>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z
-Z</t>
-        </is>
-      </c>
+      <c r="F5" s="21"/>
       <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∼
-‹</t>
+          <t xml:space="preserve">潢∼</t>
         </is>
       </c>
       <c r="I5" s="24"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J5" s="21"/>
       <c r="K5" s="24"/>
     </row>
     <row r="6" ht="90.2" customHeight="true">
@@ -2321,11 +2310,7 @@
         </is>
       </c>
       <c r="E6" s="22"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F6" s="21"/>
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
@@ -2378,31 +2363,27 @@
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∼
-‹</t>
+          <t xml:space="preserve">潢∼</t>
         </is>
       </c>
       <c r="K8" s="24"/>
@@ -2457,8 +2438,7 @@
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="E10" s="23"/>
@@ -2467,8 +2447,7 @@
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="I10" s="23"/>
@@ -2487,29 +2466,23 @@
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢ʒ</t>
+潢</t>
         </is>
       </c>
       <c r="E11" s="24"/>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z
-Z</t>
-        </is>
-      </c>
+      <c r="F11" s="21"/>
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢ʒ</t>
+潢</t>
         </is>
       </c>
       <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="K11" s="24"/>
@@ -2524,11 +2497,7 @@
         </is>
       </c>
       <c r="E12" s="22"/>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F12" s="21"/>
       <c r="G12" s="22"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
@@ -2574,8 +2543,7 @@
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="G14" s="24"/>

--- a/sheets/조재수대금교본/검수/어디로 가야하나.xlsx
+++ b/sheets/조재수대금교본/검수/어디로 가야하나.xlsx
@@ -2288,7 +2288,12 @@
         </is>
       </c>
       <c r="E5" s="24"/>
-      <c r="F5" s="21"/>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z
+Z</t>
+        </is>
+      </c>
       <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
@@ -2310,7 +2315,11 @@
         </is>
       </c>
       <c r="E6" s="22"/>
-      <c r="F6" s="21"/>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
@@ -2466,16 +2475,21 @@
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢</t>
+潢ʒ</t>
         </is>
       </c>
       <c r="E11" s="24"/>
-      <c r="F11" s="21"/>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z
+Z</t>
+        </is>
+      </c>
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢</t>
+潢ʒ</t>
         </is>
       </c>
       <c r="I11" s="24"/>
@@ -2497,7 +2511,11 @@
         </is>
       </c>
       <c r="E12" s="22"/>
-      <c r="F12" s="21"/>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G12" s="22"/>
       <c r="H12" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/어디로 가야하나.xlsx
+++ b/sheets/조재수대금교본/검수/어디로 가야하나.xlsx
@@ -2179,22 +2179,22 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="50.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="74.33" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="74.33" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="74.33" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -2304,7 +2304,7 @@
       <c r="J5" s="21"/>
       <c r="K5" s="24"/>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="74.33" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="K6" s="22"/>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="74.33" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="K7" s="23"/>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="74.33" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="K8" s="24"/>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="74.33" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="K9" s="22"/>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="74.33" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="K10" s="23"/>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="74.33" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="K11" s="24"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="74.33" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="K12" s="22"/>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="74.33" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -2543,7 +2543,7 @@
       <c r="J13" s="21"/>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="74.33" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -2576,6 +2576,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="80"/>
 </worksheet>
 </file>